--- a/data/data/puertos.xlsx
+++ b/data/data/puertos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelson/planInfra/data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF149892-7256-48B7-BAAE-628F1955D88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F074D8-2A8C-FC47-AE19-F8178A7DDE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -126,12 +126,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -146,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,7 +166,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,9 +453,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,11 +469,11 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -470,11 +483,11 @@
       <c r="C2" s="4">
         <v>200700</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="6">
         <v>0.20369999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -484,11 +497,11 @@
       <c r="C3" s="4">
         <v>120000</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="6">
         <v>0.12180000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
@@ -498,11 +511,11 @@
       <c r="C4" s="4">
         <v>104000</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>0.1055</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -512,11 +525,11 @@
       <c r="C5" s="4">
         <v>91000</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>9.2299999999999993E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -526,11 +539,11 @@
       <c r="C6" s="4">
         <v>82992</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <v>8.4199999999999997E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -540,11 +553,11 @@
       <c r="C7" s="4">
         <v>74900</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -554,11 +567,11 @@
       <c r="C8" s="4">
         <v>65400</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6">
         <v>6.6400000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -568,11 +581,11 @@
       <c r="C9" s="4">
         <v>65120</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
         <v>6.6100000000000006E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -582,11 +595,11 @@
       <c r="C10" s="4">
         <v>60000</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="6">
         <v>6.0900000000000003E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
@@ -596,11 +609,11 @@
       <c r="C11" s="4">
         <v>35000</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="6">
         <v>3.5499999999999997E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
@@ -610,11 +623,11 @@
       <c r="C12" s="4">
         <v>30306</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="6">
         <v>3.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -624,11 +637,11 @@
       <c r="C13" s="4">
         <v>30000</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="6">
         <v>3.04E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>24</v>
       </c>
@@ -638,7 +651,7 @@
       <c r="C14" s="4">
         <v>26000</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="6">
         <v>2.64E-2</v>
       </c>
     </row>
